--- a/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/data/D3_threshold_library.xlsx
+++ b/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/data/D3_threshold_library.xlsx
@@ -336,7 +336,7 @@
     <t>physical_contract_v2.7.0</t>
   </si>
   <si>
-    <t>v2.7.0</t>
+    <t>v2.8.0</t>
   </si>
 </sst>
 </file>
